--- a/public/download/ozon-tul-vual-ДЮНА-zapolnennyy.xlsx
+++ b/public/download/ozon-tul-vual-ДЮНА-zapolnennyy.xlsx
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AG5" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 290 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH5" s="4" t="n"/>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AG6" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 260 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH6" s="4" t="n"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AG7" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 255 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH7" s="4" t="n"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AG8" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 230 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH8" s="4" t="n"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AG9" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 235 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH9" s="4" t="n"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AG10" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 230 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH10" s="4" t="n"/>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 270 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH11" s="4" t="n"/>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 240 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH12" s="4" t="n"/>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 235 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH13" s="4" t="n"/>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 245 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH14" s="4" t="n"/>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 245 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH15" s="4" t="n"/>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 230 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH16" s="4" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 270 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH17" s="4" t="n"/>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AG18" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 265 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH18" s="4" t="n"/>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 260 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH19" s="4" t="n"/>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AG20" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 275 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH20" s="4" t="n"/>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="AG21" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 250 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH21" s="4" t="n"/>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AG22" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 280 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH22" s="4" t="n"/>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 285 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH23" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 280 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH24" s="4" t="n"/>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 275 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH25" s="4" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 235 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH26" s="4" t="n"/>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 250 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH27" s="4" t="n"/>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AG28" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 260 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH28" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 290 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH29" s="4" t="n"/>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AG30" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 265 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH30" s="4" t="n"/>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="AG31" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 255 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH31" s="4" t="n"/>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AG32" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 240 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH32" s="4" t="n"/>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AG33" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 280 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH33" s="4" t="n"/>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="AG34" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 230 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH34" s="4" t="n"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="AG35" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 280 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH35" s="4" t="n"/>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="AG36" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 245 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH36" s="4" t="n"/>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AG37" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 245 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH37" s="4" t="n"/>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AG38" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 235 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH38" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AG39" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 280 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH39" s="4" t="n"/>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="AG40" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 230 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH40" s="4" t="n"/>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="AG41" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 235 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH41" s="4" t="n"/>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="AG42" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 275 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH42" s="4" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AG43" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 295 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH43" s="4" t="n"/>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AG44" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 290 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH44" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="AG45" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 265 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH45" s="4" t="n"/>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AG46" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 245 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH46" s="4" t="n"/>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AG47" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 240 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH47" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="AG48" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 275 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH48" s="4" t="n"/>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="AG49" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 255 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH49" s="4" t="n"/>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="AG50" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 240 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH50" s="4" t="n"/>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="AG51" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 220 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 220 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 220 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH51" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="AG52" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 285 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH52" s="4" t="n"/>
@@ -11517,7 +11517,7 @@
       </c>
       <c r="AG53" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 275 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH53" s="4" t="n"/>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="AG54" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 290 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH54" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="AG55" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 230 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH55" s="4" t="n"/>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG56" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 225 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 225 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 225 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH56" s="4" t="n"/>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="AG57" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 295 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH57" s="4" t="n"/>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="AG58" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 235 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH58" s="4" t="n"/>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="AG59" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 255 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH59" s="4" t="n"/>
@@ -12973,7 +12973,7 @@
       </c>
       <c r="AG60" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 285 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH60" s="4" t="n"/>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="AG61" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 240 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH61" s="4" t="n"/>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="AG62" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 270 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH62" s="4" t="n"/>
@@ -13597,7 +13597,7 @@
       </c>
       <c r="AG63" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 245 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH63" s="4" t="n"/>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="AG64" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 285 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH64" s="4" t="n"/>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="AG65" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 290 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH65" s="4" t="n"/>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="AG66" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 230 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH66" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="AG67" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 255 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH67" s="4" t="n"/>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="AG68" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 285 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH68" s="4" t="n"/>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AG69" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 265 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH69" s="4" t="n"/>
@@ -15053,7 +15053,7 @@
       </c>
       <c r="AG70" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 265 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH70" s="4" t="n"/>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="AG71" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 295 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH71" s="4" t="n"/>
@@ -15469,7 +15469,7 @@
       </c>
       <c r="AG72" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 250 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH72" s="4" t="n"/>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="AG73" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 285 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH73" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="AG74" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 245 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH74" s="4" t="n"/>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="AG75" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 290 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH75" s="4" t="n"/>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="AG76" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 275 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH76" s="4" t="n"/>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="AG77" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 260 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH77" s="4" t="n"/>
@@ -16717,7 +16717,7 @@
       </c>
       <c r="AG78" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 290 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH78" s="4" t="n"/>
@@ -16925,7 +16925,7 @@
       </c>
       <c r="AG79" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 270 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH79" s="4" t="n"/>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="AG80" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 280 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH80" s="4" t="n"/>
@@ -17341,7 +17341,7 @@
       </c>
       <c r="AG81" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 250 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH81" s="4" t="n"/>
@@ -17549,7 +17549,7 @@
       </c>
       <c r="AG82" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 240 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH82" s="4" t="n"/>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="AG83" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 235 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH83" s="4" t="n"/>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="AG84" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 250 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH84" s="4" t="n"/>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="AG85" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 280 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH85" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="AG86" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 200 × 260 см.", "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня.", "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 200 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH86" s="4" t="n"/>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AG87" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 270 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH87" s="4" t="n"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="AG88" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 265 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH88" s="4" t="n"/>
@@ -19005,7 +19005,7 @@
       </c>
       <c r="AG89" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 285 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH89" s="4" t="n"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="AG90" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 295 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH90" s="4" t="n"/>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="AG91" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 295 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH91" s="4" t="n"/>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="AG92" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 240 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH92" s="4" t="n"/>
@@ -19837,7 +19837,7 @@
       </c>
       <c r="AG93" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 270 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH93" s="4" t="n"/>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="AG94" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 255 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH94" s="4" t="n"/>
@@ -20253,7 +20253,7 @@
       </c>
       <c r="AG95" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 255 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH95" s="4" t="n"/>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="AG96" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 250 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH96" s="4" t="n"/>
@@ -20669,7 +20669,7 @@
       </c>
       <c r="AG97" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 400 × 250 см.", "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м.", "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 400 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH97" s="4" t="n"/>
@@ -20877,7 +20877,7 @@
       </c>
       <c r="AG98" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 270 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH98" s="4" t="n"/>
@@ -21085,7 +21085,7 @@
       </c>
       <c r="AG99" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 260 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH99" s="4" t="n"/>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="AG100" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 800 × 220 см.", "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м.", "ВЫСОТА — от карниза до пола. 220 см — короткая, до подоконника: удобно на кухню и когда под окном батарея.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 800 × 220 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH100" s="4" t="n"/>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="AG101" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 700 × 260 см.", "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м.", "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 700 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH101" s="4" t="n"/>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="AG102" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 600 × 275 см.", "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд.", "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 600 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH102" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="AG103" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 500 × 265 см.", "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м.", "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 500 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH103" s="4" t="n"/>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="AG104" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Тюль вуаль молочная ДЮНА"]}, "text": {"size": "size2", "align": "left", "content": ["Готовая штора на окно: повесить можно сразу из упаковки.", "Молочный оттенок мягче холодного белого — он не желтит, не серит и сочетается со шторами любого цвета: бежевыми, серыми, графитовыми, зелёными."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Матовая вуаль без блеска"]}, "text": {"size": "size2", "align": "left", "content": ["Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м².", "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."]}}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Шторная лента 4 см, две нити"]}, "text": {"size": "size2", "align": "left", "content": ["Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки.", "Подходит для карнизов с крючками, круглых и профильных.", "Боковой шов — ролевой: тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Как выбрать размер"]}, "text": {"size": "size2", "align": "left", "content": ["Ваш размер: 300 × 295 см.", "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м.", "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха.", "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."]}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}, {"widgetName": "raTextBlock", "align": "left", "padding": "p_10", "title": {"size": "size3", "align": "left", "content": ["Уход и комплектация"]}, "text": {"size": "size2", "align": "left", "content": ["Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима.", "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом.", "В комплекте: тюль 300 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."]}}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH104" s="4" t="n"/>

--- a/public/download/ozon-tul-vual-ДЮНА-zapolnennyy.xlsx
+++ b/public/download/ozon-tul-vual-ДЮНА-zapolnennyy.xlsx
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AG5" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×290 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 290 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH5" s="4" t="n"/>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AG6" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×260 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 260 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH6" s="4" t="n"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AG7" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×255 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 255 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH7" s="4" t="n"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="AG8" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×230 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 230 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH8" s="4" t="n"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AG9" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×235 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 235 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH9" s="4" t="n"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AG10" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×230 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 230 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH10" s="4" t="n"/>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×270 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 270 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH11" s="4" t="n"/>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×240 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 240 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH12" s="4" t="n"/>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×235 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 235 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH13" s="4" t="n"/>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×245 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 245 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH14" s="4" t="n"/>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×245 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 245 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH15" s="4" t="n"/>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×230 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 230 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH16" s="4" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×270 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 270 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH17" s="4" t="n"/>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AG18" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×265 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 265 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH18" s="4" t="n"/>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×260 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 260 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH19" s="4" t="n"/>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AG20" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×275 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 275 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH20" s="4" t="n"/>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="AG21" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×250 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 250 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH21" s="4" t="n"/>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AG22" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×280 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 280 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH22" s="4" t="n"/>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×285 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 285 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH23" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×280 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 280 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH24" s="4" t="n"/>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×275 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 275 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH25" s="4" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×235 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 235 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH26" s="4" t="n"/>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×250 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 250 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH27" s="4" t="n"/>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="AG28" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×260 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 260 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH28" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×290 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 290 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH29" s="4" t="n"/>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AG30" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×265 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 265 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH30" s="4" t="n"/>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="AG31" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×255 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 255 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH31" s="4" t="n"/>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AG32" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×240 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 240 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH32" s="4" t="n"/>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AG33" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×280 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 280 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH33" s="4" t="n"/>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="AG34" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×230 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 230 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH34" s="4" t="n"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="AG35" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×280 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 280 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH35" s="4" t="n"/>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="AG36" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×245 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 245 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH36" s="4" t="n"/>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AG37" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×245 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 245 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH37" s="4" t="n"/>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AG38" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×235 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 235 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH38" s="4" t="n"/>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AG39" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×280 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 280 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH39" s="4" t="n"/>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="AG40" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×230 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 230 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH40" s="4" t="n"/>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="AG41" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×235 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 235 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH41" s="4" t="n"/>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="AG42" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×275 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 275 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH42" s="4" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AG43" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×295 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 295 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH43" s="4" t="n"/>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AG44" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×290 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 290 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH44" s="4" t="n"/>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="AG45" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×265 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 265 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH45" s="4" t="n"/>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AG46" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×245 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 245 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH46" s="4" t="n"/>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AG47" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×240 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 240 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH47" s="4" t="n"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="AG48" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×275 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 275 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH48" s="4" t="n"/>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="AG49" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×255 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 255 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH49" s="4" t="n"/>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="AG50" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×240 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 240 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH50" s="4" t="n"/>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="AG51" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×220 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 220 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 220 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 220 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH51" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="AG52" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×285 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 285 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH52" s="4" t="n"/>
@@ -11517,7 +11517,7 @@
       </c>
       <c r="AG53" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×275 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 275 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH53" s="4" t="n"/>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="AG54" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×290 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 290 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH54" s="4" t="n"/>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="AG55" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×230 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 230 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH55" s="4" t="n"/>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG56" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×225 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 225 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 225 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 225 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH56" s="4" t="n"/>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="AG57" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×295 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 295 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH57" s="4" t="n"/>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="AG58" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×235 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 235 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH58" s="4" t="n"/>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="AG59" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×255 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 255 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH59" s="4" t="n"/>
@@ -12973,7 +12973,7 @@
       </c>
       <c r="AG60" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×285 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 285 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH60" s="4" t="n"/>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="AG61" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×240 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 240 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH61" s="4" t="n"/>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="AG62" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×270 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 270 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH62" s="4" t="n"/>
@@ -13597,7 +13597,7 @@
       </c>
       <c r="AG63" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×245 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 245 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH63" s="4" t="n"/>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="AG64" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×285 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 285 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH64" s="4" t="n"/>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="AG65" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×290 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 290 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH65" s="4" t="n"/>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="AG66" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×230 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 230 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 230 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 230 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH66" s="4" t="n"/>
@@ -14429,7 +14429,7 @@
       </c>
       <c r="AG67" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×255 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 255 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH67" s="4" t="n"/>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="AG68" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×285 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 285 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH68" s="4" t="n"/>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AG69" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×265 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 265 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH69" s="4" t="n"/>
@@ -15053,7 +15053,7 @@
       </c>
       <c r="AG70" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×265 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 265 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH70" s="4" t="n"/>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="AG71" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×295 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 295 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH71" s="4" t="n"/>
@@ -15469,7 +15469,7 @@
       </c>
       <c r="AG72" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×250 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 250 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH72" s="4" t="n"/>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="AG73" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×285 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 285 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH73" s="4" t="n"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="AG74" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×245 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 245 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 245 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 245 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH74" s="4" t="n"/>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="AG75" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×290 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 290 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH75" s="4" t="n"/>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="AG76" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×275 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 275 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH76" s="4" t="n"/>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="AG77" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×260 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 260 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH77" s="4" t="n"/>
@@ -16717,7 +16717,7 @@
       </c>
       <c r="AG78" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×290 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 290 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 290 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 290 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH78" s="4" t="n"/>
@@ -16925,7 +16925,7 @@
       </c>
       <c r="AG79" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×270 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 270 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH79" s="4" t="n"/>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="AG80" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×280 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 280 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH80" s="4" t="n"/>
@@ -17341,7 +17341,7 @@
       </c>
       <c r="AG81" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×250 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 250 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH81" s="4" t="n"/>
@@ -17549,7 +17549,7 @@
       </c>
       <c r="AG82" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×240 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 240 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH82" s="4" t="n"/>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="AG83" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×235 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 235 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 235 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 235 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH83" s="4" t="n"/>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="AG84" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×250 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 250 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH84" s="4" t="n"/>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="AG85" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×280 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 280 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 280 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 280 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH85" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="AG86" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 200×260 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 200 см рассчитана на узкое окно, балконную дверь или половину стандартного проёма: полотно ложится лёгкими складками без лишнего объёма."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 200 × 260 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 200 см — узкое окно, балконная дверь, кухня."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 200 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH86" s="4" t="n"/>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AG87" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×270 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 270 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH87" s="4" t="n"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="AG88" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×265 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 265 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH88" s="4" t="n"/>
@@ -19005,7 +19005,7 @@
       </c>
       <c r="AG89" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×285 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 285 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 285 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 285 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH89" s="4" t="n"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="AG90" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×295 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 295 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH90" s="4" t="n"/>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="AG91" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×295 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 295 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH91" s="4" t="n"/>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="AG92" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×240 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 240 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 240 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 240 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH92" s="4" t="n"/>
@@ -19837,7 +19837,7 @@
       </c>
       <c r="AG93" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×270 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 270 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH93" s="4" t="n"/>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="AG94" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×255 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 255 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH94" s="4" t="n"/>
@@ -20253,7 +20253,7 @@
       </c>
       <c r="AG95" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×255 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 255 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 255 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 255 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH95" s="4" t="n"/>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="AG96" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×250 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 250 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH96" s="4" t="n"/>
@@ -20669,7 +20669,7 @@
       </c>
       <c r="AG97" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 400×250 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 400 см рассчитана на окно с балконной дверью или проём до 2 м: полотно ложится красивой плотной сборкой по всей ширине."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 400 × 250 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 400 см — окно с балконной дверью, проём до 2 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 250 см — в пол при потолках 2,6–2,8 м."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 400 × 250 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH97" s="4" t="n"/>
@@ -20877,7 +20877,7 @@
       </c>
       <c r="AG98" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×270 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 270 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 270 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 270 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH98" s="4" t="n"/>
@@ -21085,7 +21085,7 @@
       </c>
       <c r="AG99" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×260 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 260 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH99" s="4" t="n"/>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="AG100" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 800×220 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 800 см рассчитана на панорамное остекление или стену целиком до 4 м: полотно ложится максимально пышной сборкой без просветов."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 800 × 220 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 800 см — панорамное остекление, стена до 4 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 220 см — короткая, до подоконника: удобно на кухню и когда под окном батарея."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 800 × 220 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH100" s="4" t="n"/>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="AG101" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 700×260 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тюль полностью готов — распаковали, надели на карниз, повесили."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 700 см рассчитана на панорамное окно или эркер 3–3,5 м: полотно ложится роскошной густой драпировкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 700 × 260 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 700 см — панорамное окно, эркер 3–3,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 260 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 700 × 260 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH101" s="4" t="n"/>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="AG102" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 600×275 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовое изделие: подшито, обработано, с пришитой шторной лентой."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 600 см рассчитана на широкий проём 2,5–3 м или два окна подряд: полотно ложится объёмной дворцовой сборкой."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 600 × 275 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 600 см — проём 2,5–3 м или два окна подряд."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 275 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 600 × 275 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH102" s="4" t="n"/>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="AG103" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 500×265 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Штора приходит готовой к карнизу — ничего доделывать не нужно."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 500 см рассчитана на широкое окно 2,2–2,5 м: полотно ложится глубокой пышной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 500 × 265 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 500 см — широкое окно 2,2–2,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 265 см — в пол при потолках 2,8–3,0 м, с запасом на подгиб."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 500 × 265 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH103" s="4" t="n"/>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="AG104" s="4" t="inlineStr">
         <is>
-          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-g/14970249052.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-2/14970249722.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}, {"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-y/14970249178.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}}]}], "version": 0.3}</t>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-b/14970250055.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Тюль вуаль молочная 300×295 см"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Готовая штора на окно: повесить можно сразу из упаковки."}, {"type": "text", "content": "Молочный оттенок мягче холодного белого: он не желтит, не серит и сочетается со шторами любого цвета — бежевыми, серыми, графитовыми, зелёными."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-h/14970249557.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Матовая вуаль без блеска"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкая полупрозрачная ткань без рисунка, плотность 80 г/м²."}, {"type": "text", "content": "Пропускает дневной свет, но скрывает комнату от взглядов с улицы. Не электризуется и не притягивает пыль."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249167.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Шторная лента 4 см, две нити"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Верх обработан тесьмой с двумя хлопковыми нитями — сборку регулируете сами, от лёгкой волны до плотной драпировки."}, {"type": "text", "content": "Подходит для карнизов с крючками, круглых и профильных."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-n/14970249743.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Боковой шов — ролевой"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Тонкий аккуратный край без утолщений и торчащих ниток. Низ ровный, подшитый."}, {"type": "text", "content": "Ширина 300 см рассчитана на стандартное окно 1,3–1,5 м: полотно ложится мягкой равномерной волной."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-f/14970249051.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Как выбрать размер"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Ваш размер: 300 × 295 см."}, {"type": "text", "content": "ШИРИНА — измерьте длину карниза. 300 см — стандартное окно 1,3–1,5 м."}, {"type": "text", "content": "ВЫСОТА — от карниза до пола. 295 см — под высокие потолки от 3,0 м, в пол до самого верха."}, {"type": "text", "content": "Для пышной сборки берите ширину в 2–2,5 раза больше длины карниза."}]}}]}, {"widgetName": "raShowcase", "type": "billboard", "blocks": [{"imgLink": "", "img": {"src": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "srcMobile": "https://cdn1.ozone.ru/s3/multimedia-1-3/14970249435.jpg", "alt": "", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1440, "heightMobile": 720}, "title": {"items": [{"type": "text", "content": "Уход и комплектация"}], "size": "size4", "align": "left", "color": "color1"}, "text": {"size": "size2", "align": "left", "color": "color1", "items": [{"type": "text", "content": "Стирка при 30 °C в деликатном режиме, отжим минимальный или без отжима."}, {"type": "text", "content": "Гладить тёплым утюгом через ткань или повесить влажной — вуаль расправляется сама под собственным весом."}, {"type": "text", "content": "В комплекте: тюль 300 × 295 см — 1 шт. Фирменная упаковка ДЮНА: zip-пакет, в котором штору удобно хранить и доставать без складок и заломов."}]}}]}], "version": 0.3}</t>
         </is>
       </c>
       <c r="AH104" s="4" t="n"/>
